--- a/public/investor-pack/Global-Office-Financial-Model.xlsx
+++ b/public/investor-pack/Global-Office-Financial-Model.xlsx
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="12">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14">
@@ -1040,7 +1040,7 @@
         <v>0.05</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="19">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="22">

--- a/public/investor-pack/Global-Office-Financial-Model.xlsx
+++ b/public/investor-pack/Global-Office-Financial-Model.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>1.2</v>
